--- a/content/Lectures/Semester 2/Week 01 - Introduction to Simulation/3 Tutorial/Tutorial Example.xlsx
+++ b/content/Lectures/Semester 2/Week 01 - Introduction to Simulation/3 Tutorial/Tutorial Example.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimailderbyac-my.sharepoint.com/personal/tcsr529_derby_ac_uk/Documents/_Teaching/202526/5CM522 - Operational Research/Lectures/Semester 2/Week 1 - Introduction to Simulation/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="103" documentId="11_F25DC773A252ABDACC104844319B7A1C5BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F31DDB59-8D2F-46E1-8B93-B1D45C1DD978}"/>
   <bookViews>
     <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
